--- a/experiment2/B200_ops_benchmark.xlsx
+++ b/experiment2/B200_ops_benchmark.xlsx
@@ -28,6 +28,11 @@
     <sheet name="18_cumsum" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="19_topk" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="20_embedding" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="21_bmm" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="22_addmm" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="23_mv" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="24_fp8_matmul" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="25_fused_linear_cross_entropy" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_unified_attention'!$A$4:$T$24</definedName>
@@ -50,6 +55,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'18_cumsum'!$A$4:$T$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'19_topk'!$A$4:$T$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'20_embedding'!$A$4:$T$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'21_bmm'!$A$4:$T$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'22_addmm'!$A$4:$T$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'23_mv'!$A$4:$T$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'24_fp8_matmul'!$A$4:$T$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'25_fused_linear_cross_entropy'!$A$4:$T$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -526,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -643,7 +653,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12 09:51</t>
+          <t>2026-10-13 03:24</t>
         </is>
       </c>
     </row>
@@ -1892,37 +1902,332 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>21_bmm</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>bmm (批量矩阵乘)</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>矩阵乘</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Triton</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>注意力QK^T/PV逐头bmm、批量Linear</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>py3.11(kaixin) + torch2.11.0+cu128</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>710.123</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>4466.43</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>6.2 ~ 25,688.3</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>20/20 OK</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>22_addmm</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>addmm (偏置融合GEMM)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>矩阵乘</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Triton</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Linear层 y=x@W+b (投影/FFN)</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>py3.11(kaixin) + torch2.11.0+cu128</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>1026.897</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>5344.03</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>6.2 ~ 10,255.1</t>
+        </is>
+      </c>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>20/20 OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>23_mv</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>mv (矩阵-向量乘)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>矩阵乘</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Triton</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>decode阶段Linear (GEMV)</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>py3.11(kaixin) + torch2.11.0+cu128</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>5.013</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>5013.98</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>6.1 ~ 957.9</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>20/20 OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>24_fp8_matmul</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>fp8_matmul (MXFP8量化GEMM)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>矩阵乘</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Triton</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>FP8低精度GEMM (128分块scale, 量化LLM推理)</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>py3.11(kaixin) + torch2.11.0+cu128</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>940.422</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>2962.59</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>8.2 ~ 12,319.8</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>20/20 OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>25_fused_linear_cross_entropy</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>fused_linear_cross_entropy</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>矩阵乘融合</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Triton</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>LLM训练输出层: lm_head GEMM+CE融合, 免logits物化</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>py3.11(kaixin) + torch2.11.0+cu128</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>1369.314</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>5174.03</v>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>110.2 ~ 31,408.6</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>20/20 OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>注1</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>unified_attention 为 vLLM v1 统一注意力接口的 Triton 实现 (vllm.v1.attention.ops.triton_unified_attention), paged KV cache + varlen query, causal。</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>注2</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>rope 的 decode 档使用 S=2 (投机解码 verify 场景): Liger-Kernel v0.8.4 的 rope 在 B&gt;1 且 S=1 时 transpose 后 stride 语义不符 (q.stride(1)=D 而非 H*D), 上游限制, 已规避。</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>注3</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>flash_attention 为 flash_attn 2.8.3 CUDA kernel (FA2); 统一 causal=True (bottom-right 对齐, Sq=1 时等价于 attend 全部上下文)。</t>
         </is>
@@ -25052,6 +25357,9183 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>bmm (批量矩阵乘)  —  FlagOpen/FlagGems v5.0.2  —  NVIDIA B200 (SM100), bf16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>计时: CUDA Event, 每次rep前清空L2(256MB), 自适应迭代; TFLOPS=FLOPs模型/时延, GB/s=Bytes模型/时延; 峰值参考: BF16 dense 2250 TFLOPS / HBM3e 8000 GB/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>no.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>规模档位</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>shape</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>维度明细</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>dtype</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>元素量</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>FLOPs(模型)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Bytes(模型)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>时延 mean (us)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>时延 min (us)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>时延 p50 (us)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>迭代次数</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>TFLOPS</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>带宽 (GB/s)</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>TFLOPS峰值占比%</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>带宽峰值占比%</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>绝对误差</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>相对误差</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>正确性</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>来源仓库</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>S-b1</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>(1,1024,1024) x (1,1024,1024)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>B=1, M=1024, K=1024, N=1024</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1,048,576</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>2,147,483,648</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>6,291,456</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>17.824</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>18.432</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>279</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>114.292</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>334.84</v>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>4.949e-01</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>3.213e-03</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>(8,512,512) x (8,512,512)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>B=8, M=512, K=512, N=512</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>2,097,152</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>2,147,483,648</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>12,582,912</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>14.577</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>13.696</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>14.336</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>279</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>147.319</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>863.2</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>2.499e-01</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>2.073e-03</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>(16,256,256) x (16,256,256)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>B=16, M=256, K=256, N=256</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1,048,576</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>536,870,912</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>6,291,456</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>10.293</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>9.632</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>52.157</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>611.22</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>2.486e-01</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>3.064e-03</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>M-head</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>(32,128,128) x (32,128,128)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>B=32, M=128, K=128, N=128</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>524,288</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>134,217,728</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>3,145,728</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>8.254</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>7.136</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>8.192</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>16.261</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>381.11</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>1.249e-01</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>2.352e-03</t>
+        </is>
+      </c>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>(8,1024,1024) x (8,1024,1024)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>B=8, M=1024, K=1024, N=1024</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>8,388,608</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>17,179,869,184</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>50,331,648</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>43.024</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>43.008</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>399.313</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>1169.86</v>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>4.999e-01</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>2.912e-03</t>
+        </is>
+      </c>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>(4,2048,2048) x (4,2048,2048)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>B=4, M=2048, K=2048, N=2048</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>16,777,216</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>68,719,476,736</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>100,663,296</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>109.531</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>106.496</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>108.576</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>627.398</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>919.04</v>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="P10" s="11" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>5.004e-01</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>1.970e-03</t>
+        </is>
+      </c>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>(2,4096,4096) x (2,4096,4096)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>B=2, M=4096, K=4096, N=4096</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>33,554,432</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>274,877,906,944</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>201,326,592</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>387.085</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>382.912</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>385.024</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>710.123</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>520.11</v>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>1.001e+00</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>2.806e-03</t>
+        </is>
+      </c>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>(1,8192,8192) x (1,8192,8192)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>B=1, M=8192, K=8192, N=8192</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>67,108,864</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>1,099,511,627,776</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>402,653,184</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>1558.022</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>1532.928</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>1537.536</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>705.71</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>258.44</v>
+      </c>
+      <c r="O12" s="11" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>1.004e+00</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>2.079e-03</t>
+        </is>
+      </c>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>L-attnQK</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>(32,4096,128) x (32,128,4096)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>B=32, M=4096, K=128, N=4096</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>536,870,912</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>137,438,953,472</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>1,140,850,688</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>491.555</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>489.44</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>489.536</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>279.601</v>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>2320.9</v>
+      </c>
+      <c r="O13" s="11" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>2.454e-01</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>3.302e-03</t>
+        </is>
+      </c>
+      <c r="S13" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>L-attnPV</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>(32,4096,4096) x (32,4096,128)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>B=32, M=4096, K=4096, N=128</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>16,777,216</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>137,438,953,472</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>1,140,850,688</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>255.428</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>251.968</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>253.952</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>538.074</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>4466.43</v>
+      </c>
+      <c r="O14" s="11" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>1.001e+00</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>2.769e-03</t>
+        </is>
+      </c>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>M-attn</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>(16,2048,128) x (16,128,2048)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>B=16, M=2048, K=128, N=2048</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>67,108,864</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>17,179,869,184</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>150,994,944</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>69.798</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>67.584</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>69.63200000000001</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>246.136</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>2163.3</v>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>1.923e-01</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>2.759e-03</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>M-b64</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>(64,1024,64) x (64,64,1024)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>B=64, M=1024, K=64, N=1024</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>67,108,864</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>8,589,934,592</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>150,994,944</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>59.589</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>58.976</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>59.36</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>144.154</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>2533.96</v>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>1.250e-01</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>2.628e-03</t>
+        </is>
+      </c>
+      <c r="S16" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>M-b128</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>(128,64,64) x (128,64,64)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>B=128, M=64, K=64, N=64</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>524,288</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>67,108,864</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>3,145,728</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>6.271</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>5.376</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>6.144</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>10.702</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>501.64</v>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>1.221e-01</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>3.054e-03</t>
+        </is>
+      </c>
+      <c r="S17" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>S-b256</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>(256,32,32) x (256,32,32)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>B=256, M=32, K=32, N=32</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>262,144</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>16,777,216</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>1,572,864</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>5.632</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>6.144</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>2.702</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>253.27</v>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>6.244e-02</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>2.145e-03</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>narrow-b1024</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>(1024,16,16) x (1024,16,16)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>B=1024, M=16, K=16, N=16</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>262,144</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>8,388,608</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>1,572,864</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>6.242</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>5.344</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>6.144</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>251.99</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>6.105e-02</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>2.750e-03</t>
+        </is>
+      </c>
+      <c r="S19" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>narrow-b4096</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>(4096,8,8) x (4096,8,8)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>B=4096, M=8, K=8, N=8</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>262,144</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>4,194,304</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>1,572,864</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>14.428</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>13.664</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>14.336</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>109.02</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>3.708e-02</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>2.114e-03</t>
+        </is>
+      </c>
+      <c r="S20" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>narrow-M1</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>(1,1,4096) x (1,4096,4096)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>B=1, M=1, K=4096, N=4096</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>4,096</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>33,554,432</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>33,570,816</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>55.38</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>55.328</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>606.2</v>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>4.981e-01</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>1.943e-03</t>
+        </is>
+      </c>
+      <c r="S21" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>narrow-tall</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>(1,131072,64) x (1,64,64)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>B=1, M=131072, K=64, N=64</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>8,388,608</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>1,073,741,824</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>33,562,624</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>14.368</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>12.288</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>14.336</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>74.73099999999999</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>2335.93</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>1.247e-01</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>2.604e-03</t>
+        </is>
+      </c>
+      <c r="S22" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>L-tall</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>(2,65536,128) x (2,128,128)</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>B=2, M=65536, K=128, N=128</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>16,777,216</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>4,294,967,296</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>67,174,400</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>22.528</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>24.608</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>175.09</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>2738.45</v>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>34.23</v>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>1.250e-01</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>1.967e-03</t>
+        </is>
+      </c>
+      <c r="S23" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>(16,8192,8192) x (16,8192,8192)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>B=16, M=8192, K=8192, N=8192</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>1,073,741,824</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>17,592,186,044,416</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>6,442,450,944</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>25688.264</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>25503.807</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>25630.239</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>684.8339999999999</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>250.79</v>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>1.951e+00</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>3.398e-03</t>
+        </is>
+      </c>
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:T24"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>addmm (偏置融合GEMM)  —  FlagOpen/FlagGems v5.0.2  —  NVIDIA B200 (SM100), bf16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>计时: CUDA Event, 每次rep前清空L2(256MB), 自适应迭代; TFLOPS=FLOPs模型/时延, GB/s=Bytes模型/时延; 峰值参考: BF16 dense 2250 TFLOPS / HBM3e 8000 GB/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>no.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>规模档位</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>shape</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>维度明细</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>dtype</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>元素量</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>FLOPs(模型)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Bytes(模型)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>时延 mean (us)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>时延 min (us)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>时延 p50 (us)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>迭代次数</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>TFLOPS</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>带宽 (GB/s)</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>TFLOPS峰值占比%</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>带宽峰值占比%</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>绝对误差</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>相对误差</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>正确性</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>来源仓库</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>(128,128) x (128,128) + (128,)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>M=128, K=128, N=128, bias=128</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>16,384</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>4,210,688</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>98,560</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>6.183</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>5.728</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>6.144</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>1.245e-01</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>2.687e-03</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>(256,256) x (256,256) + (256,)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>M=256, K=256, N=256, bias=256</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>65,536</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>33,619,968</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>393,728</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>8.211</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>7.232</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>8.192</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>4.095</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>2.412e-01</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>3.393e-03</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>(512,512) x (512,512) + (512,)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>M=512, K=512, N=512, bias=512</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>262,144</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>268,697,600</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>1,573,888</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>10.213</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>154.11</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>2.500e-01</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>2.180e-03</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>(1024,1024) x (1024,1024) + (1024,)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>M=1024, K=1024, N=1024, bias=1024</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1,048,576</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>2,148,532,224</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>6,293,504</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>14.566</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>13.728</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>14.336</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>279</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>147.501</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>432.06</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>4.948e-01</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>2.851e-03</t>
+        </is>
+      </c>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>(2048,2048) x (2048,2048) + (2048,)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>M=2048, K=2048, N=2048, bias=2048</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>4,194,304</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>17,184,063,488</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>25,169,920</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>28.464</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>28.672</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>603.722</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>884.29</v>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>5.003e-01</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>2.166e-03</t>
+        </is>
+      </c>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>(4096,4096) x (4096,4096) + (4096,)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=4096, N=4096, bias=4096</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>16,777,216</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>137,455,730,688</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>100,671,488</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>159.281</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>157.632</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>159.712</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>862.978</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>632.04</v>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="P10" s="11" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>9.985e-01</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>2.969e-03</t>
+        </is>
+      </c>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>(8192,8192) x (8192,8192) + (8192,)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>M=8192, K=8192, N=8192, bias=8192</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>67,108,864</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>1,099,578,736,640</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>402,669,568</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>1102.216</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>1067.008</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>1113.024</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>997.6079999999999</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>365.33</v>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>1.004e+00</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>1.875e-03</t>
+        </is>
+      </c>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>(16384,16384) x (16384,16384) + (16384,)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>M=16384, K=16384, N=16384, bias=16384</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>268,435,456</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>8,796,361,457,664</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>1,610,645,504</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>10255.146</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>10081.216</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>10268.64</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>857.751</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>157.06</v>
+      </c>
+      <c r="O12" s="11" t="n">
+        <v>38.12</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>2.012e+00</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>2.714e-03</t>
+        </is>
+      </c>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>M-llamaFFN</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>(4096,4096) x (4096,11008) + (11008,)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=4096, N=11008, bias=11008</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>45,088,768</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>369,412,276,224</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>213,931,520</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>359.736</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>354.272</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>359.456</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>1026.897</v>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>594.6900000000001</v>
+      </c>
+      <c r="O13" s="11" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>1.001e+00</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>2.544e-03</t>
+        </is>
+      </c>
+      <c r="S13" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>(8192,4096) x (4096,4096) + (4096,)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>M=8192, K=4096, N=4096, bias=4096</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>33,554,432</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>274,911,461,376</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>167,780,352</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>292.381</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>288.48</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>292.768</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>940.249</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>573.84</v>
+      </c>
+      <c r="O14" s="11" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>1.001e+00</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>2.636e-03</t>
+        </is>
+      </c>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>(4096,11008) x (11008,4096) + (4096,)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=11008, N=4096, bias=4096</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>16,777,216</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>369,383,964,672</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>213,917,696</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>387.517</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>378.88</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>383.968</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>953.206</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>552.02</v>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>1.541e+00</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>2.716e-03</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>narrow-GEMV</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>(1,4096) x (4096,4096) + (4096,)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>M=1, K=4096, N=4096, bias=4096</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>4,096</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>33,558,528</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>33,579,008</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>32.352</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>34.816</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>970.5</v>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>7.629e-01</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>2.943e-03</t>
+        </is>
+      </c>
+      <c r="S16" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>narrow-batch</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>(8,16384) x (16384,16384) + (16384,)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>M=8, K=16384, N=16384, bias=16384</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>131,072</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>4,295,098,368</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>537,427,968</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>138.389</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>139.168</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>31.036</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>3883.45</v>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>1.981e+00</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>2.923e-03</t>
+        </is>
+      </c>
+      <c r="S17" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>narrow-tall</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>(131072,64) x (64,64) + (64,)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>M=131072, K=64, N=64, bias=64</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>8,388,608</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>1,082,130,432</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>33,562,752</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>18.063</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>16.288</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>18.432</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>1858.14</v>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>1.250e-01</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>2.752e-03</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>narrow-K</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>(64,131072) x (131072,64) + (64,)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>M=64, K=131072, N=64, bias=64</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>4,096</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>1,073,745,920</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>33,562,752</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>827.8579999999999</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>825.216</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>827.456</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>3.643e+00</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>2.342e-03</t>
+        </is>
+      </c>
+      <c r="S19" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>tall-thin</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>(32768,128) x (128,128) + (128,)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>M=32768, K=128, N=128, bias=128</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>4,194,304</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>1,077,936,128</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>16,810,240</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>12.291</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>11.712</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>12.288</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>87.703</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>1367.71</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>1.250e-01</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>1.796e-03</t>
+        </is>
+      </c>
+      <c r="S20" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>thin-K</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>(128,32768) x (32768,128) + (128,)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>M=128, K=32768, N=128, bias=128</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>16,384</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>1,073,758,208</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>16,810,240</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>210.773</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>208.768</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>210.944</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>5.094</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>2.012e+00</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>2.792e-03</t>
+        </is>
+      </c>
+      <c r="S21" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>(65536,64) x (64,4096) + (4096,)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>M=65536, K=64, N=4096, bias=4096</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>268,435,456</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>34,628,173,824</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>545,792,000</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>288.335</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>286.688</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>288.704</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>120.097</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>1892.91</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>1.250e-01</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>2.480e-03</t>
+        </is>
+      </c>
+      <c r="S22" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>wide</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>(64,4096) x (4096,65536) + (65536,)</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>M=64, K=4096, N=65536, bias=65536</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>4,194,304</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>34,363,932,672</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>545,914,880</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>102.154</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>102.432</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>336.393</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>5344.03</v>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>9.967e-01</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>2.834e-03</t>
+        </is>
+      </c>
+      <c r="S23" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>(4096,5120) x (5120,5120) + (5120,)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=5120, N=5120, bias=5120</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>20,971,520</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>214,769,336,320</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>136,325,120</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>236.829</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>231.36</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>237.504</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>906.852</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>575.63</v>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>1.001e+00</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>2.451e-03</t>
+        </is>
+      </c>
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:T24"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>mv (矩阵-向量乘)  —  FlagOpen/FlagGems v5.0.2  —  NVIDIA B200 (SM100), bf16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>计时: CUDA Event, 每次rep前清空L2(256MB), 自适应迭代; TFLOPS=FLOPs模型/时延, GB/s=Bytes模型/时延; 峰值参考: BF16 dense 2250 TFLOPS / HBM3e 8000 GB/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>no.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>规模档位</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>shape</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>维度明细</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>dtype</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>元素量</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>FLOPs(模型)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Bytes(模型)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>时延 mean (us)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>时延 min (us)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>时延 p50 (us)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>迭代次数</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>TFLOPS</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>带宽 (GB/s)</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>TFLOPS峰值占比%</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>带宽峰值占比%</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>绝对误差</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>相对误差</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>正确性</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>来源仓库</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>(128,1024) x (1024,)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>M=128, K=1024</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>262,144</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>264,448</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>6.398</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>6.144</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>2.401e-01</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>2.989e-03</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>(1024,1024) x (1024,)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>M=1024, K=1024</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1,024</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>2,097,152</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>2,101,248</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>7.806</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>5.696</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>8.192</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>269.19</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>2.492e-01</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>2.332e-03</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>XS-thinK</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>(1024,128) x (128,)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>M=1024, K=128</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1,024</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>262,144</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>264,448</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>6.142</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>5.248</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>6.144</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>1.249e-01</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>2.784e-03</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>(4096,1024) x (1024,)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=1024</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>4,096</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>8,388,608</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>8,398,848</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>8.228</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>7.648</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>8.192</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>1020.81</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>2.494e-01</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>2.272e-03</t>
+        </is>
+      </c>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>(4096,4096) x (4096,)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=4096</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>4,096</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>33,554,432</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>33,570,816</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>14.339</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>13.312</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>14.336</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>2341.3</v>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>4.965e-01</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>1.979e-03</t>
+        </is>
+      </c>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>M-llamaFFN</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>(11008,4096) x (4096,)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>M=11008, K=4096</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>11,008</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>90,177,536</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>90,207,744</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>30.305</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>28.288</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>2.976</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>2976.63</v>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P10" s="11" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>4.998e-01</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>2.099e-03</t>
+        </is>
+      </c>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>M-llamaDown</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>(4096,11008) x (11008,)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=11008</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>4,096</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>90,177,536</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>90,207,744</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>30.169</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>28.288</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>2.989</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>2990.1</v>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>9.700e-01</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>2.531e-03</t>
+        </is>
+      </c>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>(8192,8192) x (8192,)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>M=8192, K=8192</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>8,192</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>134,217,728</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>134,250,496</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>38.922</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>37.888</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>38.944</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>3.448</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>3449.2</v>
+      </c>
+      <c r="O12" s="11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>43.11</v>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>9.805e-01</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>2.837e-03</t>
+        </is>
+      </c>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>(5120,5120) x (5120,)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>M=5120, K=5120</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>5,120</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>52,428,800</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>52,449,280</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>22.432</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>22.528</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>2.337</v>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>2338.12</v>
+      </c>
+      <c r="O13" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>4.991e-01</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>1.755e-03</t>
+        </is>
+      </c>
+      <c r="S13" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>(2048,2048) x (2048,)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>M=2048, K=2048</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>2,048</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>8,388,608</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>8,396,800</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>10.001</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>8.096</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>839.59</v>
+      </c>
+      <c r="O14" s="11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>4.648e-01</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>2.589e-03</t>
+        </is>
+      </c>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>(16384,16384) x (16384,)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>M=16384, K=16384</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>16,384</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>536,870,912</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>536,936,448</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>107.088</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>105.568</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>106.56</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>5.013</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>5013.98</v>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>1.120e+00</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>1.941e-03</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>(12288,12288) x (12288,)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>M=12288, K=12288</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>12,288</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>301,989,888</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>302,039,040</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>70.73999999999999</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>69.248</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>71.55200000000001</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>4.269</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>4269.68</v>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>9.965e-01</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>2.199e-03</t>
+        </is>
+      </c>
+      <c r="S16" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>narrow-M1</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>(1,4096) x (4096,)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>M=1, K=4096</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>8,192</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>16,386</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>9.253</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>7.808</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>10.048</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>9.742e-02</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>1.537e-03</t>
+        </is>
+      </c>
+      <c r="S17" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>narrow-K1</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>(4096,1) x (1,)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=1</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>4,096</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>8,192</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>16,386</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>6.197</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>5.568</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>6.144</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>5.005e-03</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>2.292e-03</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>narrow-longK</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>(1,1048576) x (1048576,)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>M=1, K=1048576</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>2,097,152</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>4,194,306</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>957.938</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>953.312</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>957.472</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>3.674e-02</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>1.044e-04</t>
+        </is>
+      </c>
+      <c r="S19" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>narrow-M1M</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>(1048576,1) x (1,)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>M=1048576, K=1</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>1,048,576</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>2,097,152</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>4,194,306</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>73.66800000000001</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>73.72799999999999</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>1.938e-03</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>2.132e-03</t>
+        </is>
+      </c>
+      <c r="S20" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>narrow-tallM</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>(131072,64) x (64,)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>M=131072, K=64</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>131,072</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>16,777,216</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>17,039,488</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>14.307</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>13.248</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>14.336</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>1.173</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>1191.02</v>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>1.237e-01</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>3.231e-03</t>
+        </is>
+      </c>
+      <c r="S21" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>narrow-tallK</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>(64,131072) x (131072,)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>M=64, K=131072</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>16,777,216</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>17,039,488</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>131.034</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>128.96</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>131.072</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>130.04</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>3.153e+00</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>2.036e-03</t>
+        </is>
+      </c>
+      <c r="S22" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>tallM</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>(65536,64) x (64,)</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>M=65536, K=64</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>65,536</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>8,388,608</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>8,519,808</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>10.233</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>8.224</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>832.5599999999999</v>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>1.234e-01</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>3.536e-03</t>
+        </is>
+      </c>
+      <c r="S23" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>tallM2</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>(32768,128) x (128,)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>M=32768, K=128</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>32,768</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>8,388,608</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>8,454,400</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>7.744</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>8.192</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>1031.63</v>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>1.249e-01</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>2.585e-03</t>
+        </is>
+      </c>
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:T24"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>fp8_matmul (MXFP8量化GEMM)  —  FlagOpen/FlagGems v5.0.2  —  NVIDIA B200 (SM100), bf16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>计时: CUDA Event, 每次rep前清空L2(256MB), 自适应迭代; TFLOPS=FLOPs模型/时延, GB/s=Bytes模型/时延; 峰值参考: BF16 dense 2250 TFLOPS / HBM3e 8000 GB/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>no.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>规模档位</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>shape</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>维度明细</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>dtype</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>元素量</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>FLOPs(模型)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Bytes(模型)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>时延 mean (us)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>时延 min (us)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>时延 p50 (us)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>迭代次数</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>TFLOPS</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>带宽 (GB/s)</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>TFLOPS峰值占比%</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>带宽峰值占比%</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>绝对误差</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>相对误差</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>正确性</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>来源仓库</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>(128,128) x (128,128) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>M=128, K=128, N=128, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>16,384</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>4,194,304</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>66,052</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>8.154</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>5.664</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>8.192</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>1.250e-01</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>2.418e-03</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>(256,256) x (256,256) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>M=256, K=256, N=256, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>65,536</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>33,554,432</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>264,208</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>6.176</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>8.192</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>4.087</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>1.878e-01</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>2.568e-03</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>(512,512) x (512,512) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>M=512, K=512, N=512, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>262,144</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>268,435,456</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>1,056,832</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>8.231999999999999</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>7.744</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>8.192</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>32.608</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>128.38</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>2.493e-01</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>2.405e-03</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>(1024,1024) x (1024,1024) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>M=1024, K=1024, N=1024, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1,048,576</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>2,147,483,648</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>4,227,328</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>12.116</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>9.792</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>12.288</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>279</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>177.246</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>348.91</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>4.966e-01</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>3.237e-03</t>
+        </is>
+      </c>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>(2048,2048) x (2048,2048) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>M=2048, K=2048, N=2048, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>4,194,304</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>17,179,869,184</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>16,909,312</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>27.959</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>26.144</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>26.656</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>614.47</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>604.79</v>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>5.002e-01</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>2.000e-03</t>
+        </is>
+      </c>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>(4096,4096) x (4096,4096) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=4096, N=4096, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>16,777,216</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>137,438,953,472</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>67,637,248</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>155.617</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>155.68</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>883.186</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>434.64</v>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="P10" s="11" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>9.982e-01</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>2.972e-03</t>
+        </is>
+      </c>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>(8192,8192) x (8192,8192) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>M=8192, K=8192, N=8192, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>67,108,864</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>1,099,511,627,776</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>270,548,992</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>1295.025</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>1234.912</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>1295.392</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>849.028</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>208.91</v>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>1.001e+00</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>1.943e-03</t>
+        </is>
+      </c>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>(16384,16384) x (16384,16384) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>M=16384, K=16384, N=16384, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>268,435,456</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>8,796,093,022,208</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>1,082,195,968</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>12319.803</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>12089.376</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>12355.456</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>713.98</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="O12" s="11" t="n">
+        <v>31.73</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>2.002e+00</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>2.609e-03</t>
+        </is>
+      </c>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>M-llamaFFN</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>(4096,4096) x (4096,11008) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=4096, N=11008, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>45,088,768</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>369,367,187,456</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>152,578,816</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>440.155</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>422.944</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>448.64</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>839.175</v>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>346.65</v>
+      </c>
+      <c r="O13" s="11" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>9.993e-01</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>2.752e-03</t>
+        </is>
+      </c>
+      <c r="S13" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>(8192,4096) x (4096,4096) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>M=8192, K=4096, N=4096, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>33,554,432</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>274,877,906,944</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>118,493,184</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>318.7</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>308.864</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>323.616</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>862.499</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="O14" s="11" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>1.000e+00</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>2.828e-03</t>
+        </is>
+      </c>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>(4096,11008) x (11008,4096) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=11008, N=4096, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>16,777,216</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>369,367,187,456</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>125,152,000</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>434.171</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>419.84</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>434.24</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>850.741</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>288.26</v>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>1.997e+00</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>3.398e-03</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>narrow-GEMV</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>(1,4096) x (4096,4096) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>M=1, K=4096, N=4096, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>4,096</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>33,554,432</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>16,793,728</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>35.214</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>34.848</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>476.9</v>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>4.998e-01</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>2.139e-03</t>
+        </is>
+      </c>
+      <c r="S16" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>narrow-batch</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>(8,16384) x (16384,16384) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>M=8, K=16384, N=16384, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>131,072</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>4,294,967,296</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>268,898,304</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>92.943</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>89.72799999999999</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>92.224</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>46.211</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>2893.16</v>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>36.16</v>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>1.937e+00</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>3.222e-03</t>
+        </is>
+      </c>
+      <c r="S17" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>narrow-tall</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>(131072,128) x (128,128) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>M=131072, K=128, N=128, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>16,777,216</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>4,294,967,296</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>50,872,324</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>32.768</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>34.816</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>123.559</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>1463.51</v>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>2.413e-01</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>3.639e-03</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>narrow-K</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>(128,131072) x (131072,128) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>M=128, K=131072, N=128, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>16,384</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>4,294,967,296</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>34,115,584</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>469.763</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>466.976</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>469.536</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>9.143000000000001</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>3.949e+00</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>2.632e-03</t>
+        </is>
+      </c>
+      <c r="S19" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>tall-thin</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>(32768,128) x (128,128) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>M=32768, K=128, N=128, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>4,194,304</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>1,073,741,824</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>12,730,372</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>12.288</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>14.336</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>75.035</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>889.62</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>1.250e-01</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>2.126e-03</t>
+        </is>
+      </c>
+      <c r="S20" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>thin-K</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>(128,32768) x (32768,128) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>M=128, K=32768, N=128, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>16,384</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>1,073,741,824</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>8,553,472</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>122.876</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>120.768</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>122.88</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>8.738</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>69.61</v>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>1.989e+00</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>2.787e-03</t>
+        </is>
+      </c>
+      <c r="S21" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>(65536,128) x (128,4096) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>M=65536, K=128, N=4096, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>268,435,456</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>68,719,476,736</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>546,046,080</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>456.451</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>454.656</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>456.704</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>150.552</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>1196.29</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>2.324e-01</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>3.377e-03</t>
+        </is>
+      </c>
+      <c r="S22" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>wide</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>(128,4096) x (4096,65536) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>M=128, K=4096, N=65536, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>8,388,608</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>68,719,476,736</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>285,818,880</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>96.476</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>95.80800000000001</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>96.288</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>712.295</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>2962.59</v>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>9.953e-01</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>2.840e-03</t>
+        </is>
+      </c>
+      <c r="S23" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>(4096,5120) x (5120,5120) fp8-blk128</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>M=4096, K=5120, N=5120, quant=MXFP8-128</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>20,971,520</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>214,748,364,800</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>89,790,720</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>228.353</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>225.312</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>228.992</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>940.422</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>393.21</v>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>1.000e+00</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>2.510e-03</t>
+        </is>
+      </c>
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>FlagOpen/FlagGems v5.0.2 (Triton)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:T24"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>fused_linear_cross_entropy  —  linkedin/Liger-Kernel v0.8.4  —  NVIDIA B200 (SM100), bf16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>计时: CUDA Event, 每次rep前清空L2(256MB), 自适应迭代; TFLOPS=FLOPs模型/时延, GB/s=Bytes模型/时延; 峰值参考: BF16 dense 2250 TFLOPS / HBM3e 8000 GB/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>no.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>规模档位</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>shape</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>维度明细</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>dtype</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>元素量</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>FLOPs(模型)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Bytes(模型)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>时延 mean (us)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>时延 min (us)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>时延 p50 (us)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>迭代次数</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>TFLOPS</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>带宽 (GB/s)</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>TFLOPS峰值占比%</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>带宽峰值占比%</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>绝对误差</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>相对误差</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>正确性</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>来源仓库</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>input=(1,4096) x weight=(32000,4096)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>T=1, H=4096, V=32000</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>32,000</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>262,304,000</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>262,152,196</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>110.194</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>103.456</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>108.576</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>2379.01</v>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>4.630e-01</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>1.612e-03</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>XS-1tok</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>input=(1,4096) x weight=(128256,4096)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>T=1, H=4096, V=128256</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>128,256</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>1,051,314,432</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>1,050,681,348</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>233.687</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>222.24</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>228.384</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>4.499</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>4496.1</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>1.132e-01</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>3.820e-04</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>input=(128,1024) x weight=(32000,1024)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>T=128, H=1024, V=32000</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>4,096,000</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>8,409,088,000</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>65,798,656</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>742.482</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>722.4640000000001</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>740.192</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>11.326</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>88.62</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>5.460e-01</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>2.594e-03</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>input=(1024,1024) x weight=(32000,1024)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>T=1024, H=1024, V=32000</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>32,768,000</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>67,272,704,000</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>67,637,248</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>753.978</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>736.896</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>748.96</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>89.224</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>6.351e-01</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>2.537e-03</t>
+        </is>
+      </c>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>input=(1024,2048) x weight=(32000,2048)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>T=1024, H=2048, V=32000</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>32,768,000</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>134,381,568,000</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>135,270,400</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>584.777</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>578.592</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>583.712</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>229.8</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>231.32</v>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>6.663e-01</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>1.885e-03</t>
+        </is>
+      </c>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>input=(1024,4096) x weight=(32000,4096)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>T=1024, H=4096, V=32000</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>32,768,000</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>268,599,296,000</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>270,536,704</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>533.903</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>529.4400000000001</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>533.5359999999999</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>503.086</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>506.71</v>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="P10" s="11" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>1.171e+00</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>2.514e-03</t>
+        </is>
+      </c>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>input=(2048,4096) x weight=(32000,4096)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>T=2048, H=4096, V=32000</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>65,536,000</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>537,198,592,000</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>278,929,408</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>682.957</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>677.92</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>680.992</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>786.578</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>408.41</v>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>1.411e+00</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>2.856e-03</t>
+        </is>
+      </c>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>input=(2048,4096) x weight=(128256,4096)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>T=2048, H=4096, V=128256</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>262,668,288</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>2,153,091,956,736</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>1,067,458,560</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>6282.877</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>6252.576</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>6282.304</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>342.692</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="O12" s="11" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>1.295e+00</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>2.488e-03</t>
+        </is>
+      </c>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>input=(4096,4096) x weight=(32000,4096)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>T=4096, H=4096, V=32000</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>131,072,000</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>1,074,397,184,000</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>295,714,816</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>953.741</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>924.704</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>958.4640000000001</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>1126.509</v>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>310.06</v>
+      </c>
+      <c r="O13" s="11" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>1.378e+00</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>2.970e-03</t>
+        </is>
+      </c>
+      <c r="S13" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>input=(4096,4096) x weight=(50257,4096)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>T=4096, H=4096, V=50257</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>205,852,672</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>1,687,374,352,384</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>445,276,160</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>13547.387</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>13535.264</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>13543.488</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>124.553</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="O14" s="11" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>2.064e+00</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>3.865e-03</t>
+        </is>
+      </c>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>input=(4096,4096) x weight=(128256,4096)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>T=4096, H=4096, V=128256</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>525,336,576</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>4,306,183,913,472</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>1,084,243,968</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>6727.941</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>6665.216</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>6731.776</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>640.045</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>161.16</v>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>1.406e+00</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>2.487e-03</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>input=(8192,4096) x weight=(128256,4096)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>T=8192, H=4096, V=128256</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>1,050,673,152</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>8,612,367,826,944</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>1,117,814,784</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>10556.769</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>10424.352</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>10551.296</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>815.8150000000001</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>105.89</v>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>1.449e+00</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>2.687e-03</t>
+        </is>
+      </c>
+      <c r="S16" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>input=(8192,2048) x weight=(32000,2048)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>T=8192, H=2048, V=32000</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>262,144,000</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>1,075,052,544,000</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>164,659,200</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>1287.484</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>1217.536</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>1335.328</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>835.003</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>127.89</v>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>9.429e-01</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>2.623e-03</t>
+        </is>
+      </c>
+      <c r="S17" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>XL-longT</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>input=(65536,1024) x weight=(32000,1024)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>T=65536, H=1024, V=32000</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>2,097,152,000</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>4,305,453,056,000</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>200,015,872</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>5179.544</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>5133.312</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>5176.352</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>831.242</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>7.266e-01</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>2.614e-03</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>XL-narrowH</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>input=(65536,512) x weight=(32000,512)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>T=65536, H=512, V=32000</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>2,097,152,000</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>2,157,969,408,000</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>100,139,008</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>3687.375</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>3671.072</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>3686.432</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>585.232</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>4.886e-01</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>2.537e-03</t>
+        </is>
+      </c>
+      <c r="S19" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>narrow-H</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>input=(262144,256) x weight=(32000,256)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>T=262144, H=256, V=32000</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>8,388,608,000</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>4,336,910,336,000</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>151,650,304</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>11548.587</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>11528.224</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>11549.728</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>375.536</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>3.690e-01</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>2.527e-03</t>
+        </is>
+      </c>
+      <c r="S20" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>narrow-1tok-wide</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>input=(1,8192) x weight=(152064,8192)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>T=1, H=8192, V=152064</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>152,064</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>2,492,176,896</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>2,491,432,964</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>481.527</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>472.064</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>481.28</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>241</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>5.176</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>5174.03</v>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>8.253e-01</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>1.926e-03</t>
+        </is>
+      </c>
+      <c r="S21" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>input=(16384,2048) x weight=(50257,2048)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>T=16384, H=2048, V=50257</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>823,410,688</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>3,376,807,231,488</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>273,027,072</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>31408.567</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>31373.312</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>31406.113</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>107.512</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>1.640e+00</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>4.157e-03</t>
+        </is>
+      </c>
+      <c r="S22" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>input=(32768,1024) x weight=(32000,1024)</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>T=32768, H=1024, V=32000</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>1,048,576,000</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>2,152,726,528,000</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>132,775,936</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>2741.885</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>2700.32</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>2756.64</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>785.126</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>34.89</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>7.374e-01</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>2.718e-03</t>
+        </is>
+      </c>
+      <c r="S23" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>input=(8192,5120) x weight=(32000,5120)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>T=8192, H=5120, V=32000</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>bf16</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>262,144,000</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>2,685,665,280,000</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>411,598,848</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>1961.322</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>1880.128</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>1889.28</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>1369.314</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>209.86</v>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>1.478e+00</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>2.633e-03</t>
+        </is>
+      </c>
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>linkedin/Liger-Kernel v0.8.4 (Triton)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:T24"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
